--- a/AAII_Financials/Quarterly/MLYBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MLYBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="92">
   <si>
     <t>MLYBY</t>
   </si>
@@ -656,74 +656,77 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -769,8 +772,11 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -816,8 +822,11 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -863,8 +872,11 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -882,8 +894,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -929,8 +942,11 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -976,8 +992,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1023,8 +1042,11 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1070,8 +1092,11 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1086,8 +1111,9 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1133,8 +1159,11 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1180,8 +1209,11 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1199,8 +1231,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1246,8 +1279,11 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1293,8 +1329,11 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1340,8 +1379,11 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1387,8 +1429,11 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1434,8 +1479,11 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1481,8 +1529,11 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1528,8 +1579,11 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1575,8 +1629,11 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1622,8 +1679,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1669,8 +1729,11 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1716,8 +1779,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1763,8 +1829,11 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1810,8 +1879,11 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1857,8 +1929,11 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1904,8 +1979,11 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1951,60 +2029,66 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2022,8 +2106,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2041,431 +2126,459 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7639000</v>
+      </c>
+      <c r="E41" s="3">
         <v>7969600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6977500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9183000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>10901600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7595700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9062800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8612800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6379400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8018100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6300600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7890400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7227400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6365400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8578500</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>23512400</v>
+      </c>
+      <c r="E42" s="3">
         <v>22747200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>26189200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>22538300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>23992000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>22598000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>25605300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>24300200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>22771900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>21920100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>22740500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>19915800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>22011000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>24379500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>21721100</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6059200</v>
+      </c>
+      <c r="E43" s="3">
         <v>5715900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3957500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5620600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5445600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5314400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3133400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5903300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3578300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2736400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2300400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4297500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3409100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3278100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2296900</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>66300</v>
+      </c>
+      <c r="E44" s="3">
         <v>68300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>84200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>79400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>83200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>82600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>85100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>91700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>82700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>89100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>94200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>91800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>93100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>95900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>93300</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3200900</v>
+      </c>
+      <c r="E45" s="3">
         <v>3209600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3184900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3241800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3008800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2971300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3045700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3335100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2863000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2900600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3022800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2739500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2595300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2617700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2614700</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>43724900</v>
+      </c>
+      <c r="E46" s="3">
         <v>42822500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>43562400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>43995500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>46566600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>42370900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>45016500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>46285100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>39280100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>39191800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>38255900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>38671800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>39033300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>39897200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>38674500</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>51258800</v>
+      </c>
+      <c r="E47" s="3">
         <v>49299300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>47452400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>48502500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>48156600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>49580000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>45493400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>48706600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>45288100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>46330000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>47099900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>45268200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>44561000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>45532800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>44251700</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1053600</v>
+      </c>
+      <c r="E48" s="3">
         <v>1076400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1079400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1037600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1049300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1006900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>836300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>896800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>827400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>825400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>860000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>806200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>824900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>888500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>757700</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1550800</v>
+      </c>
+      <c r="E49" s="3">
         <v>1590100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1609000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1567800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1592000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1540100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1564000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1635100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1523300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1549600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1604800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1554200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1548200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1541400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1540400</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2511,8 +2624,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2558,55 +2674,61 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1475400</v>
+      </c>
+      <c r="E52" s="3">
         <v>1539600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1596400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1586000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1596600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1477200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1579900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1767000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1597000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1559400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1511500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>320000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>362200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>344900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1993200</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2652,55 +2774,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>264490900</v>
+      </c>
+      <c r="E54" s="3">
         <v>260409700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>259509700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>253553400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>254780500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>244067100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>240494300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>254833800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>225480500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>223835600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>224016300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>213298700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>211587800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>217457800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>216468100</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2718,8 +2846,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2737,290 +2866,309 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>189723500</v>
+      </c>
+      <c r="E57" s="3">
         <v>187604300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>188101100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>186074600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>187942400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>179099500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>175659600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>184145700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>160289400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>160078100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>159974900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>151511500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>148920600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>155940200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>156235700</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>16414500</v>
+        <v>9193400</v>
       </c>
       <c r="E58" s="3">
+        <v>8955700</v>
+      </c>
+      <c r="F58" s="3">
         <v>16004300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>12483800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>13497600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>14921000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>16965700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>17403700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>17696200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>17167900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>18264900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>10739600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>9363200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>8466900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>13444100</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>565300</v>
+      </c>
+      <c r="E59" s="3">
         <v>443200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>455200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>474400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>455000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>371200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>337500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>414700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>318400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>362500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>299200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>325200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>350100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>292200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>498500</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>207056800</v>
+        <v>202441800</v>
       </c>
       <c r="E60" s="3">
+        <v>199598000</v>
+      </c>
+      <c r="F60" s="3">
         <v>206200100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>201807900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>204336700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>196404900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>193990500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>204422500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>179890700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>179244800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>179629600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>164068100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>160150100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>166235900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>171665800</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>10361100</v>
+        <v>17948400</v>
       </c>
       <c r="E61" s="3">
+        <v>17819900</v>
+      </c>
+      <c r="F61" s="3">
         <v>9398900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9651200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8386700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8494400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7576400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9036700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8464400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8021200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7266500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>14627900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>16386700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>15550100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8818600</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>20184100</v>
+      </c>
+      <c r="E62" s="3">
         <v>19546900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>19748700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>18982400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>18612800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>17307300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>16899600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>18337200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>16047400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>15807700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>15570700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>14294900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>14805000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>15291300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>15580200</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3066,8 +3214,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3113,8 +3264,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3160,55 +3314,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>240853200</v>
+      </c>
+      <c r="E66" s="3">
         <v>237245500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>235656500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>230750600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>231643900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>222490300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>218754000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>232102400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>204667000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>203326400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>202730600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>193233200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>191588200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>197302000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>196237000</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3226,8 +3386,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3273,8 +3434,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3320,8 +3484,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3367,8 +3534,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3414,55 +3584,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10174600</v>
+      </c>
+      <c r="E72" s="3">
         <v>9598100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9942300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>8947900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9181300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>8127800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8359400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8452600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7590200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7043900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7538300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6955200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7238600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7121900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7384700</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3508,8 +3684,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3555,8 +3734,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3602,55 +3784,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>22782900</v>
+      </c>
+      <c r="E76" s="3">
         <v>22312000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>23016500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>22013300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>22356100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20835400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>21016400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>21981300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20167500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>19848800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20630300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19397800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19338300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>19450300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>19576800</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3696,60 +3884,66 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3795,8 +3989,11 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3814,55 +4011,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>49000</v>
+      </c>
+      <c r="E83" s="3">
         <v>46200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>50000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>45900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>46200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>8600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>48000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>48400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>49600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>10400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>45800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>41200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>41600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>-7100</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3908,8 +4109,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3955,8 +4159,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4002,8 +4209,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4049,8 +4259,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4096,55 +4309,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3506600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-389100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>240700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2730600</v>
       </c>
-      <c r="G89" s="3">
-        <v>3744400</v>
-      </c>
       <c r="H89" s="3">
+        <v>3700500</v>
+      </c>
+      <c r="I89" s="3">
         <v>-3573300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>422000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-885500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3085200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2406600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2997600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3494500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2706900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1497600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1254800</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4162,55 +4381,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-38200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-55800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-29100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-34000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-16600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-31200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-18600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-27400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-9700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-43300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-12800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-17300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-21700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-27600</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4256,8 +4479,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4303,55 +4529,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-33600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-101000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-34100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-27800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-11100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-55600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>44300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-28300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-19600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-72000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-24900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-25300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-28600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-51100</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4369,55 +4601,59 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>984600</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>860900</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>870500</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>848900</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>791900</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>744600</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>819000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>765200</v>
       </c>
     </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4463,8 +4699,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4510,8 +4749,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4557,145 +4799,157 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3593900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-603400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1482300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1315100</v>
       </c>
-      <c r="G100" s="3">
-        <v>-160500</v>
-      </c>
       <c r="H100" s="3">
+        <v>-116600</v>
+      </c>
+      <c r="I100" s="3">
         <v>1067100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3303800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3000300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>713300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>3801300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>4901500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2195400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-614800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-794800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-924000</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-127700</v>
+      </c>
+      <c r="E101" s="3">
         <v>800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>248100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-529900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-18400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>82200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-16800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-8700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>153400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>24900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-111100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>107900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>95900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>21600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>113300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1048500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1517300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4112900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3428400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2516500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3918300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1629200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2418700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1457400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1815100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1332700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3193700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>699000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>168700</v>
       </c>
     </row>
